--- a/docs/assets/infraestructura/s2-e1-matriz-riesgos.xlsx
+++ b/docs/assets/infraestructura/s2-e1-matriz-riesgos.xlsx
@@ -777,7 +777,7 @@
         <v>Recolección no autorizada de datos personales</v>
       </c>
       <c r="D2" t="str">
-        <v>Las reglas publicadas el 22-jun-2026 permiten listar sin sesión las matrículas pagadas (nombres y teléfonos)</v>
+        <v>Las reglas publicadas el 22-jun-2026 permitían, hasta el 2026-10-24, listar sin sesión las matrículas pagadas (nombres y teléfonos)</v>
       </c>
       <c r="E2" t="str">
         <v>Exposición de datos de menores y apoderados; incumplimiento de la Ley N.° 29733</v>
@@ -809,7 +809,7 @@
         <v>Escalamiento de privilegios por un usuario registrado</v>
       </c>
       <c r="D3" t="str">
-        <v>Las reglas publicadas permiten crear un perfil de auxiliar o docente sin invitación</v>
+        <v>Las reglas publicadas hasta el 2026-10-24 permitían crear un perfil de auxiliar o docente sin invitación</v>
       </c>
       <c r="E3" t="str">
         <v>Acceso a funciones de asistencia y a datos de alumnos</v>
@@ -841,7 +841,7 @@
         <v>Interrupción de la matrícula pública</v>
       </c>
       <c r="D4" t="str">
-        <v>Las reglas publicadas bloquean la lectura y el cupo que necesita la matrícula sin sesión</v>
+        <v>Las reglas publicadas hasta el 2026-10-24 bloqueaban la lectura y el cupo que necesita la matrícula sin sesión</v>
       </c>
       <c r="E4" t="str">
         <v>Pérdida de pre-matrículas e ingresos</v>
@@ -905,7 +905,7 @@
         <v>Uso indebido de una credencial de administrador del proyecto Firebase</v>
       </c>
       <c r="D6" t="str">
-        <v>La clave de la cuenta de servicio está en copias ZIP versionadas en el repositorio privado</v>
+        <v>La clave de la cuenta de servicio estuvo en copias ZIP versionadas en el repositorio privado (revocada el 2026-10-24)</v>
       </c>
       <c r="E6" t="str">
         <v>Lectura y escritura total de datos y cuentas</v>
@@ -937,7 +937,7 @@
         <v>Acceso no autorizado a MySQL</v>
       </c>
       <c r="D7" t="str">
-        <v>Credenciales de la base local en archivos de entorno versionados</v>
+        <v>Archivos de entorno versionados (hoy sin contraseñas; el equipo decidió mantenerlos en Git)</v>
       </c>
       <c r="E7" t="str">
         <v>Lectura o alteración de la réplica</v>
@@ -1714,7 +1714,7 @@
     <col min="6" max="6" width="29.83203125" customWidth="1"/>
     <col min="7" max="7" width="16.83203125" customWidth="1"/>
     <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="39.83203125" customWidth="1"/>
+    <col min="9" max="9" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1772,7 +1772,7 @@
         <v>Bajo</v>
       </c>
       <c r="I2" t="str">
-        <v>Pendiente (corregido en código)</v>
+        <v>Tratado (2026-10-24): publicadas desde la consola; listar matrículas pagadas sin sesión → 403</v>
       </c>
     </row>
     <row r="3">
@@ -1801,7 +1801,7 @@
         <v>Bajo</v>
       </c>
       <c r="I3" t="str">
-        <v>Pendiente (corregido en código)</v>
+        <v>Tratado (2026-10-24): reglas publicadas; falta revisar los 4 perfiles existentes</v>
       </c>
     </row>
     <row r="4">
@@ -1830,7 +1830,7 @@
         <v>Bajo</v>
       </c>
       <c r="I4" t="str">
-        <v>Pendiente (corregido en código)</v>
+        <v>Tratado (2026-10-24): pre-matrícula de prueba sin sesión exitosa en producción</v>
       </c>
     </row>
     <row r="5">
@@ -1859,7 +1859,7 @@
         <v>Bajo</v>
       </c>
       <c r="I5" t="str">
-        <v>En curso (CI definido en código)</v>
+        <v>En curso: reglas publicadas desde la consola el 2026-10-24; falta el secreto del CI y la comparación mensual</v>
       </c>
     </row>
     <row r="6">
@@ -1888,7 +1888,7 @@
         <v>Medio</v>
       </c>
       <c r="I6" t="str">
-        <v>Pendiente (retiro de copias iniciado)</v>
+        <v>Tratado (2026-10-24): clave 283b43c3… eliminada y reemplazada por ddf50bfe…; falta el escaneo de secretos en el CI</v>
       </c>
     </row>
     <row r="7">
@@ -1917,7 +1917,7 @@
         <v>Bajo</v>
       </c>
       <c r="I7" t="str">
-        <v>Pendiente</v>
+        <v>Tratado con riesgo aceptado (2026-10-24): los .env no tienen contraseñas y siguen versionados por decisión del equipo; las contraseñas MySQL irán fuera de ellos</v>
       </c>
     </row>
     <row r="8">

--- a/docs/assets/infraestructura/s2-e1-matriz-riesgos.xlsx
+++ b/docs/assets/infraestructura/s2-e1-matriz-riesgos.xlsx
@@ -723,7 +723,7 @@
   <dimension ref="A1:J30"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
     <col min="3" max="3" width="60.83203125" customWidth="1"/>
     <col min="4" max="4" width="60.83203125" customWidth="1"/>
     <col min="5" max="5" width="60.83203125" customWidth="1"/>
@@ -995,16 +995,16 @@
         <v>R-08</v>
       </c>
       <c r="B9" t="str">
-        <v>ACT-19</v>
+        <v>ACT-16, ACT-17, ACT-19</v>
       </c>
       <c r="C9" t="str">
         <v>Agotamiento de memoria del VPS</v>
       </c>
       <c r="D9" t="str">
-        <v>2 GB compartidos por Nginx, PHP-FPM y PostgreSQL, sin línea base ni alertas</v>
+        <v>2 GB compartidos por Nginx, PHP-FPM, PostgreSQL y, desde el 2026-10-24, la capa de la academia; sin alertas</v>
       </c>
       <c r="E9" t="str">
-        <v>Caída del sitio y de la API del colegio</v>
+        <v>Caída del sitio y de la API del colegio y de la capa de la academia</v>
       </c>
       <c r="F9" t="str">
         <v>3</v>
@@ -1609,7 +1609,7 @@
         <v>Pérdida de los respaldos de MySQL junto con la base</v>
       </c>
       <c r="D28" t="str">
-        <v>Respaldos en el mismo equipo que la base; programación diaria no verificada</v>
+        <v>Respaldos en el mismo servidor que la base; la copia fuera del VPS es manual y semanal</v>
       </c>
       <c r="E28" t="str">
         <v>Sin recuperación ante una falla del equipo</v>
@@ -1641,7 +1641,7 @@
         <v>Réplica relacional incompleta</v>
       </c>
       <c r="D29" t="str">
-        <v>Sincroniza solo con la PC local encendida y sin reintentos</v>
+        <v>Sin reintentos: un envío que falla no se repite (INC-06); los datos anteriores a la sincronización se cargaron el 2026-10-24</v>
       </c>
       <c r="E29" t="str">
         <v>Reportes con datos faltantes</v>
@@ -1667,7 +1667,7 @@
         <v>R-29</v>
       </c>
       <c r="B30" t="str">
-        <v>ACT-13, ACT-15, ACT-19</v>
+        <v>ACT-13, ACT-15, ACT-16, ACT-17, ACT-19</v>
       </c>
       <c r="C30" t="str">
         <v>Dependencia de proveedores</v>
@@ -1960,7 +1960,7 @@
         <v>8.6, 8.16</v>
       </c>
       <c r="D9" t="str">
-        <v>Medir la línea base; no alojar la capa de la academia en el VPS; swap de 1–2 GB; alerta al 80 %; ampliar el plan si MemAvailable &lt; 25 %</v>
+        <v>Línea base medida el 2026-10-24: 1,5 GiB disponibles antes de la capa de la academia y 1,3 GiB con ella en marcha, con MySQL de bajo consumo; swap de 1 GiB; alerta al 80 %; ampliar el plan si MemAvailable &lt; 25 %</v>
       </c>
       <c r="E9" t="str">
         <v>Encargado de TI</v>
@@ -1975,7 +1975,7 @@
         <v>Medio</v>
       </c>
       <c r="I9" t="str">
-        <v>Pendiente</v>
+        <v>Tratado en parte (2026-10-24): línea base medida; faltan la alerta y el monitoreo</v>
       </c>
     </row>
     <row r="10">
@@ -2120,7 +2120,7 @@
         <v>Bajo</v>
       </c>
       <c r="I14" t="str">
-        <v>Pendiente</v>
+        <v>Tratado (2026-10-24): 5 de 5 cabeceras y versión oculta en el Nginx del colegio; cabeceras de vercel.json en la SPA</v>
       </c>
     </row>
     <row r="15">
@@ -2511,7 +2511,7 @@
         <v>8.13</v>
       </c>
       <c r="D28" t="str">
-        <v>Programar con PM2 y copiar a PBS y fuera de la sede (3-2-1)</v>
+        <v>Respaldo diario con un temporizador de systemd en el VPS y copia semanal verificada en la PC (2026-10-24); falta la copia en PBS (3-2-1)</v>
       </c>
       <c r="E28" t="str">
         <v>Líder técnico</v>
@@ -2526,7 +2526,7 @@
         <v>Bajo</v>
       </c>
       <c r="I28" t="str">
-        <v>Pendiente</v>
+        <v>Tratado en parte (2026-10-24): respaldo diario y copia semanal verificada; falta PBS</v>
       </c>
     </row>
     <row r="29">
@@ -2540,7 +2540,7 @@
         <v>8.14, 8.16</v>
       </c>
       <c r="D29" t="str">
-        <v>Servicio 24/7 en VM-APP01; conciliación con v_conciliacion_pagos; resincronización desde Firestore</v>
+        <v>Servicio 24/7 en el VPS desde el 2026-10-24 (destino de diseño: VM-APP01); conciliación con v_conciliacion_pagos; carga inicial y resincronización desde Firestore</v>
       </c>
       <c r="E29" t="str">
         <v>Líder técnico</v>
@@ -2555,7 +2555,7 @@
         <v>Bajo</v>
       </c>
       <c r="I29" t="str">
-        <v>Planificado</v>
+        <v>Tratado en parte (2026-10-24): servicio 24/7 en el VPS y carga inicial hecha; faltan los reintentos</v>
       </c>
     </row>
     <row r="30">
